--- a/Data/EXCEL/Transfer/dividend/20260215_1_2/1417-dividend-20260215_1_2.xlsx
+++ b/Data/EXCEL/Transfer/dividend/20260215_1_2/1417-dividend-20260215_1_2.xlsx
@@ -5,12 +5,12 @@
   <workbookPr defaultThemeVersion="202300"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\Workspaces\xls2xlsx\transfer\dividend\20260215_1_2(所屬年度_現金殖利率＋股票殖利率)\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\workspaces\xls2xlxs\20260215_1_2\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="8_{89D7C688-90ED-41D0-A42B-F17152FD0222}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="8_{AD91BC5B-C971-4EEB-895C-C3D07FB48278}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="9720" yWindow="2670" windowWidth="21285" windowHeight="16275" xr2:uid="{DB58C9B7-9A77-41AF-A215-BE2287977832}"/>
+    <workbookView xWindow="3492" yWindow="1344" windowWidth="16656" windowHeight="10992" xr2:uid="{C647B56B-52AD-417B-9109-A034F8FE3605}"/>
   </bookViews>
   <sheets>
     <sheet name="1417-dividend-20260215_1_2" sheetId="1" r:id="rId1"/>
@@ -1451,26 +1451,25 @@
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{7FFD2E16-94C8-4D29-88B2-123EA43D2A29}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{CBA1F1FE-A219-419F-B4CA-517291F19FA7}">
   <dimension ref="A1:X46"/>
-  <sheetFormatPr defaultRowHeight="16.5" x14ac:dyDescent="0.25"/>
+  <sheetFormatPr defaultRowHeight="16.2" x14ac:dyDescent="0.3"/>
   <cols>
-    <col min="1" max="2" width="11.375" customWidth="1"/>
-    <col min="3" max="3" width="10.25" customWidth="1"/>
-    <col min="4" max="8" width="6.25" customWidth="1"/>
-    <col min="9" max="10" width="6.625" customWidth="1"/>
-    <col min="11" max="13" width="6.25" customWidth="1"/>
-    <col min="14" max="15" width="6.625" customWidth="1"/>
-    <col min="16" max="18" width="6.25" customWidth="1"/>
-    <col min="19" max="19" width="6.625" customWidth="1"/>
-    <col min="20" max="20" width="6.25" customWidth="1"/>
-    <col min="21" max="21" width="6.625" customWidth="1"/>
-    <col min="22" max="22" width="6.25" customWidth="1"/>
-    <col min="23" max="23" width="6.625" customWidth="1"/>
-    <col min="24" max="24" width="8.25" customWidth="1"/>
+    <col min="3" max="3" width="9.109375" bestFit="1" customWidth="1"/>
+    <col min="4" max="8" width="5.5546875" bestFit="1" customWidth="1"/>
+    <col min="9" max="10" width="5.77734375" bestFit="1" customWidth="1"/>
+    <col min="11" max="13" width="5.5546875" bestFit="1" customWidth="1"/>
+    <col min="14" max="15" width="5.77734375" bestFit="1" customWidth="1"/>
+    <col min="16" max="18" width="5.5546875" bestFit="1" customWidth="1"/>
+    <col min="19" max="19" width="5.77734375" bestFit="1" customWidth="1"/>
+    <col min="20" max="20" width="5.5546875" bestFit="1" customWidth="1"/>
+    <col min="21" max="21" width="5.77734375" bestFit="1" customWidth="1"/>
+    <col min="22" max="22" width="5.5546875" bestFit="1" customWidth="1"/>
+    <col min="23" max="23" width="5.77734375" bestFit="1" customWidth="1"/>
+    <col min="24" max="24" width="5.5546875" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:24" s="1" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:24" s="1" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A1" s="18" t="s">
         <v>0</v>
       </c>
@@ -1504,7 +1503,7 @@
       <c r="W1" s="27"/>
       <c r="X1" s="19"/>
     </row>
-    <row r="2" spans="1:24" s="3" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
+    <row r="2" spans="1:24" s="3" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A2" s="20" t="s">
         <v>1</v>
       </c>
@@ -1540,7 +1539,7 @@
       <c r="W2" s="29"/>
       <c r="X2" s="30"/>
     </row>
-    <row r="3" spans="1:24" s="3" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
+    <row r="3" spans="1:24" s="3" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A3" s="20" t="s">
         <v>2</v>
       </c>
@@ -1592,7 +1591,7 @@
       </c>
       <c r="X3" s="33"/>
     </row>
-    <row r="4" spans="1:24" s="3" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
+    <row r="4" spans="1:24" s="3" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A4" s="22"/>
       <c r="B4" s="23"/>
       <c r="C4" s="7"/>
@@ -1660,7 +1659,7 @@
         <v>25</v>
       </c>
     </row>
-    <row r="5" spans="1:24" s="9" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
+    <row r="5" spans="1:24" s="9" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A5" s="34">
         <v>2024</v>
       </c>
@@ -1732,7 +1731,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="6" spans="1:24" s="13" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
+    <row r="6" spans="1:24" s="13" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A6" s="36">
         <v>2023</v>
       </c>
@@ -1804,7 +1803,7 @@
         <v>2.06</v>
       </c>
     </row>
-    <row r="7" spans="1:24" s="9" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
+    <row r="7" spans="1:24" s="9" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A7" s="34">
         <v>2022</v>
       </c>
@@ -1876,7 +1875,7 @@
         <v>3.12</v>
       </c>
     </row>
-    <row r="8" spans="1:24" s="13" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
+    <row r="8" spans="1:24" s="13" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A8" s="36">
         <v>2021</v>
       </c>
@@ -1948,7 +1947,7 @@
         <v>3.51</v>
       </c>
     </row>
-    <row r="9" spans="1:24" s="9" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
+    <row r="9" spans="1:24" s="9" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A9" s="34">
         <v>2020</v>
       </c>
@@ -2020,7 +2019,7 @@
         <v>2.88</v>
       </c>
     </row>
-    <row r="10" spans="1:24" s="13" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
+    <row r="10" spans="1:24" s="13" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A10" s="36">
         <v>2019</v>
       </c>
@@ -2092,7 +2091,7 @@
         <v>7.34</v>
       </c>
     </row>
-    <row r="11" spans="1:24" s="9" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
+    <row r="11" spans="1:24" s="9" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A11" s="34">
         <v>2018</v>
       </c>
@@ -2164,7 +2163,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="12" spans="1:24" s="13" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
+    <row r="12" spans="1:24" s="13" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A12" s="36">
         <v>2017</v>
       </c>
@@ -2236,7 +2235,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="13" spans="1:24" s="9" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
+    <row r="13" spans="1:24" s="9" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A13" s="34">
         <v>2016</v>
       </c>
@@ -2308,7 +2307,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="14" spans="1:24" s="13" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
+    <row r="14" spans="1:24" s="13" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A14" s="36">
         <v>2015</v>
       </c>
@@ -2380,7 +2379,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="15" spans="1:24" s="9" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
+    <row r="15" spans="1:24" s="9" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A15" s="34">
         <v>2014</v>
       </c>
@@ -2452,7 +2451,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="16" spans="1:24" s="13" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
+    <row r="16" spans="1:24" s="13" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A16" s="36">
         <v>2013</v>
       </c>
@@ -2524,7 +2523,7 @@
         <v>2.7</v>
       </c>
     </row>
-    <row r="17" spans="1:24" s="9" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
+    <row r="17" spans="1:24" s="9" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A17" s="34">
         <v>2012</v>
       </c>
@@ -2596,7 +2595,7 @@
         <v>5.97</v>
       </c>
     </row>
-    <row r="18" spans="1:24" s="13" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
+    <row r="18" spans="1:24" s="13" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A18" s="36">
         <v>2011</v>
       </c>
@@ -2668,7 +2667,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="19" spans="1:24" s="9" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
+    <row r="19" spans="1:24" s="9" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A19" s="34">
         <v>2010</v>
       </c>
@@ -2740,7 +2739,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="20" spans="1:24" s="13" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
+    <row r="20" spans="1:24" s="13" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A20" s="36">
         <v>2009</v>
       </c>
@@ -2812,7 +2811,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="21" spans="1:24" s="9" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
+    <row r="21" spans="1:24" s="9" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A21" s="34">
         <v>2008</v>
       </c>
@@ -2884,7 +2883,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="22" spans="1:24" s="13" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
+    <row r="22" spans="1:24" s="13" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A22" s="36">
         <v>2007</v>
       </c>
@@ -2956,7 +2955,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="23" spans="1:24" s="9" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
+    <row r="23" spans="1:24" s="9" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A23" s="34">
         <v>2006</v>
       </c>
@@ -3028,7 +3027,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="24" spans="1:24" s="13" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
+    <row r="24" spans="1:24" s="13" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A24" s="36">
         <v>2005</v>
       </c>
@@ -3100,7 +3099,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="25" spans="1:24" s="9" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
+    <row r="25" spans="1:24" s="9" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A25" s="34">
         <v>2004</v>
       </c>
@@ -3172,7 +3171,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="26" spans="1:24" s="13" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
+    <row r="26" spans="1:24" s="13" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A26" s="36">
         <v>2003</v>
       </c>
@@ -3244,7 +3243,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="27" spans="1:24" s="9" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
+    <row r="27" spans="1:24" s="9" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A27" s="34">
         <v>2002</v>
       </c>
@@ -3316,7 +3315,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="28" spans="1:24" s="13" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
+    <row r="28" spans="1:24" s="13" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A28" s="36">
         <v>2001</v>
       </c>
@@ -3388,7 +3387,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="29" spans="1:24" s="9" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
+    <row r="29" spans="1:24" s="9" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A29" s="34">
         <v>2000</v>
       </c>
@@ -3460,7 +3459,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="30" spans="1:24" s="13" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
+    <row r="30" spans="1:24" s="13" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A30" s="36">
         <v>1999</v>
       </c>
@@ -3532,7 +3531,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="31" spans="1:24" s="9" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
+    <row r="31" spans="1:24" s="9" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A31" s="34">
         <v>1998</v>
       </c>
@@ -3604,7 +3603,7 @@
         <v>12.7</v>
       </c>
     </row>
-    <row r="32" spans="1:24" s="13" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
+    <row r="32" spans="1:24" s="13" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A32" s="36">
         <v>1997</v>
       </c>
@@ -3676,7 +3675,7 @@
         <v>6.62</v>
       </c>
     </row>
-    <row r="33" spans="1:24" s="9" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
+    <row r="33" spans="1:24" s="9" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A33" s="34">
         <v>1996</v>
       </c>
@@ -3748,7 +3747,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="34" spans="1:24" s="13" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
+    <row r="34" spans="1:24" s="13" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A34" s="36">
         <v>1995</v>
       </c>
@@ -3820,7 +3819,7 @@
         <v>4.12</v>
       </c>
     </row>
-    <row r="35" spans="1:24" s="9" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
+    <row r="35" spans="1:24" s="9" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A35" s="34">
         <v>1994</v>
       </c>
@@ -3892,7 +3891,7 @@
         <v>3.76</v>
       </c>
     </row>
-    <row r="36" spans="1:24" s="13" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
+    <row r="36" spans="1:24" s="13" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A36" s="36">
         <v>1993</v>
       </c>
@@ -3964,7 +3963,7 @@
         <v>3.74</v>
       </c>
     </row>
-    <row r="37" spans="1:24" s="9" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
+    <row r="37" spans="1:24" s="9" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A37" s="34">
         <v>1992</v>
       </c>
@@ -4036,7 +4035,7 @@
         <v>6.67</v>
       </c>
     </row>
-    <row r="38" spans="1:24" s="13" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
+    <row r="38" spans="1:24" s="13" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A38" s="36">
         <v>1991</v>
       </c>
@@ -4108,7 +4107,7 @@
         <v>6.98</v>
       </c>
     </row>
-    <row r="39" spans="1:24" s="9" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
+    <row r="39" spans="1:24" s="9" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A39" s="34">
         <v>1990</v>
       </c>
@@ -4180,7 +4179,7 @@
         <v>5.21</v>
       </c>
     </row>
-    <row r="40" spans="1:24" s="13" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
+    <row r="40" spans="1:24" s="13" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A40" s="36">
         <v>1989</v>
       </c>
@@ -4252,7 +4251,7 @@
         <v>28</v>
       </c>
     </row>
-    <row r="41" spans="1:24" s="9" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
+    <row r="41" spans="1:24" s="9" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A41" s="34">
         <v>1987</v>
       </c>
@@ -4324,7 +4323,7 @@
         <v>28</v>
       </c>
     </row>
-    <row r="42" spans="1:24" s="13" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
+    <row r="42" spans="1:24" s="13" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A42" s="36">
         <v>1986</v>
       </c>
@@ -4396,7 +4395,7 @@
         <v>28</v>
       </c>
     </row>
-    <row r="43" spans="1:24" s="9" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
+    <row r="43" spans="1:24" s="9" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A43" s="34">
         <v>1985</v>
       </c>
@@ -4468,7 +4467,7 @@
         <v>28</v>
       </c>
     </row>
-    <row r="44" spans="1:24" s="13" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
+    <row r="44" spans="1:24" s="13" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A44" s="36">
         <v>1984</v>
       </c>
@@ -4540,7 +4539,7 @@
         <v>28</v>
       </c>
     </row>
-    <row r="45" spans="1:24" s="9" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
+    <row r="45" spans="1:24" s="9" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A45" s="34">
         <v>1983</v>
       </c>
@@ -4612,7 +4611,7 @@
         <v>28</v>
       </c>
     </row>
-    <row r="46" spans="1:24" s="13" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
+    <row r="46" spans="1:24" s="13" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A46" s="36" t="s">
         <v>42</v>
       </c>
